--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20685" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线4层（中）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="410">
   <si>
     <t>ID</t>
   </si>
@@ -87,6 +87,9 @@
     <t>伴随着一阵刺耳的拖地声，这扇标有B-512的沉重铁门应声弹开，手电光柱如利刃般劈开室内的黑暗，跟着的着是你们紧随其后的两支枪口。</t>
   </si>
   <si>
+    <t>8 enhanced suspence-horror</t>
+  </si>
+  <si>
     <t>false</t>
   </si>
   <si>
@@ -445,6 +448,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -2560,21 +2568,21 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" ht="27" spans="1:12">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -2592,7 +2600,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -2607,12 +2615,12 @@
         <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="54" spans="1:12">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2630,7 +2638,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -2645,12 +2653,12 @@
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:12">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2668,7 +2676,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2680,12 +2688,12 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="40.5" spans="1:12">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2703,7 +2711,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -2715,15 +2723,15 @@
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="54" spans="1:12">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2741,7 +2749,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2756,15 +2764,15 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -2779,7 +2787,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -2794,12 +2802,12 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -2817,7 +2825,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -2832,15 +2840,15 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
@@ -2855,7 +2863,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -2870,12 +2878,12 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -2908,12 +2916,12 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" ht="150" spans="1:12">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -2931,7 +2939,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -2946,15 +2954,15 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" ht="28.5" spans="1:12">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
@@ -2969,7 +2977,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -2984,12 +2992,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3022,12 +3030,12 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" ht="150" spans="1:12">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3045,7 +3053,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3057,15 +3065,15 @@
         <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3098,12 +3106,12 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" ht="150" spans="1:12">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3121,7 +3129,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3133,15 +3141,15 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
@@ -3156,7 +3164,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3171,15 +3179,15 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
@@ -3194,7 +3202,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3206,15 +3214,15 @@
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" ht="150" spans="1:12">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3232,7 +3240,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3247,15 +3255,15 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
@@ -3270,7 +3278,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3285,15 +3293,15 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -3308,7 +3316,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3323,12 +3331,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" ht="90" spans="1:12">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3346,7 +3354,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3361,12 +3369,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" ht="54" spans="1:12">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3384,7 +3392,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3396,15 +3404,15 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3437,15 +3445,15 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" ht="90" spans="1:12">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
@@ -3460,7 +3468,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3475,12 +3483,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" ht="27" spans="1:12">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3498,7 +3506,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3513,21 +3521,21 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3536,7 +3544,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3548,15 +3556,15 @@
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" ht="27" spans="1:12">
       <c r="A29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3565,7 +3573,7 @@
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -3574,7 +3582,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3586,15 +3594,15 @@
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3627,15 +3635,15 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" ht="150" spans="1:12">
       <c r="A31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
@@ -3650,7 +3658,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3665,12 +3673,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" ht="27" spans="1:12">
       <c r="A32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3688,7 +3696,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3703,15 +3711,15 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" ht="57" spans="1:12">
       <c r="A33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
@@ -3726,7 +3734,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3738,15 +3746,15 @@
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3764,7 +3772,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3779,15 +3787,15 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" ht="28.5" spans="1:12">
       <c r="A35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
@@ -3802,7 +3810,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -3817,15 +3825,15 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -3840,7 +3848,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -3855,12 +3863,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" ht="27" spans="1:12">
       <c r="A37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -3878,7 +3886,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -3893,15 +3901,15 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s">
         <v>14</v>
@@ -3916,7 +3924,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -3931,12 +3939,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" ht="55.5" spans="1:12">
       <c r="A39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -3954,7 +3962,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -3966,18 +3974,18 @@
         <v>15</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L39" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" ht="150" spans="1:12">
       <c r="A40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C40" t="s">
         <v>14</v>
@@ -3992,7 +4000,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4004,18 +4012,18 @@
         <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" ht="150" spans="1:12">
       <c r="A41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
@@ -4030,7 +4038,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4042,15 +4050,15 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42" ht="70.5" spans="1:12">
       <c r="A42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4068,7 +4076,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4083,12 +4091,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" ht="28.5" spans="1:12">
       <c r="A43" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4106,7 +4114,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4121,15 +4129,15 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B44" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
@@ -4144,7 +4152,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4159,12 +4167,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" ht="40.5" spans="1:12">
       <c r="A45" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4182,7 +4190,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4197,15 +4205,15 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" ht="28.5" spans="1:12">
       <c r="A46" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B46" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -4220,7 +4228,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4235,12 +4243,12 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" ht="27" spans="1:12">
       <c r="A47" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4258,7 +4266,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4273,21 +4281,21 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" ht="42" spans="1:12">
       <c r="A48" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4296,7 +4304,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4308,24 +4316,24 @@
         <v>15</v>
       </c>
       <c r="K48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L48" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="49" ht="40.5" spans="1:12">
       <c r="A49" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B49" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4334,7 +4342,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4346,15 +4354,15 @@
         <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" ht="150" spans="1:12">
       <c r="A50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4372,7 +4380,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4384,15 +4392,15 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4425,21 +4433,21 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" ht="90" spans="1:12">
       <c r="A52" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B52" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4448,7 +4456,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4460,15 +4468,15 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L52" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" ht="27" spans="1:12">
       <c r="A53" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4477,7 +4485,7 @@
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -4486,7 +4494,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4498,18 +4506,18 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L53" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" ht="42" spans="1:12">
       <c r="A54" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B54" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
@@ -4524,7 +4532,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4539,15 +4547,15 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B55" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
@@ -4562,7 +4570,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4577,12 +4585,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56" ht="40.5" spans="1:12">
       <c r="A56" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4600,7 +4608,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4615,15 +4623,15 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" ht="40.5" spans="1:12">
       <c r="A57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B57" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -4638,7 +4646,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4653,15 +4661,15 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58" ht="27" spans="1:12">
       <c r="A58" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
@@ -4676,7 +4684,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4691,12 +4699,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="59" ht="27" spans="1:12">
       <c r="A59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4714,7 +4722,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4729,12 +4737,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="60" ht="54" spans="1:12">
       <c r="A60" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4752,7 +4760,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4764,24 +4772,24 @@
         <v>15</v>
       </c>
       <c r="K60" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L60" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61" ht="90" spans="1:12">
       <c r="A61" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -4790,7 +4798,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4802,24 +4810,24 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L61" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="62" ht="28.5" spans="1:12">
       <c r="A62" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B62" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -4828,7 +4836,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -4840,15 +4848,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L62" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="63" ht="27" spans="1:12">
       <c r="A63" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -4866,7 +4874,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -4881,15 +4889,15 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="64" ht="42" spans="1:12">
       <c r="A64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B64" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -4904,7 +4912,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -4916,15 +4924,15 @@
         <v>15</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L64" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="65" ht="150" spans="1:12">
       <c r="A65" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -4942,7 +4950,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -4954,15 +4962,15 @@
         <v>15</v>
       </c>
       <c r="K65" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L65" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" ht="150" spans="1:12">
       <c r="A66" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -4980,7 +4988,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -4995,12 +5003,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="67" ht="55.5" spans="1:12">
       <c r="A67" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5018,7 +5026,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5033,12 +5041,12 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="68" ht="27" spans="1:12">
       <c r="A68" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5056,7 +5064,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5071,15 +5079,15 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B69" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
@@ -5094,7 +5102,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5109,15 +5117,15 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70" ht="28.5" spans="1:12">
       <c r="A70" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B70" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -5132,7 +5140,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5144,15 +5152,15 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L70" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" ht="150" spans="1:12">
       <c r="A71" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5170,7 +5178,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5182,10 +5190,10 @@
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L71" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -5206,122 +5214,122 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -5343,616 +5351,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B12" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B13" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D13" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B15" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B16" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D16" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E16" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B17" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C17" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D17" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E17" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B18" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C18" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D18" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E18" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F18" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B20" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C20" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D20" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E20" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F20" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B21" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C21" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D21" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E21" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B22" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C22" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D22" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E22" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F22" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B23" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C23" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D23" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E23" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F23" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B24" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C24" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D24" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E24" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F24" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B25" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C25" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D25" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E25" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F25" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B26" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C26" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D26" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E26" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F26" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B27" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C27" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D27" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E27" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F27" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B28" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C28" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D28" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E28" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F28" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B29" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C29" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D29" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E29" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F29" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B30" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C30" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D30" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E30" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F30" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B31" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C31" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D31" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11400"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线4层（中）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="411">
   <si>
     <t>ID</t>
   </si>
@@ -93,7 +93,7 @@
     <t>false</t>
   </si>
   <si>
-    <t>bgfade(sntzm_david4F(2)_1,1)</t>
+    <t>bgfade(sntzm_david4F(2)_1,1)&amp;unlockmusic(Music8)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=0</t>
@@ -114,6 +114,9 @@
     <t>两侧墙壁上各挂着一张闪着花白乱码的监视器屏幕，粗粝的防静电橡胶垫从角落一直延伸到房门，几根断裂的线缆从天花板无力地垂下，如同被手术刀斩断的神经末梢。</t>
   </si>
   <si>
+    <t>unlockscene(scene7)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=2</t>
   </si>
   <si>
@@ -216,7 +219,70 @@
     <t>bgfade(sntzm_david4F(2)_15,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=14; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"飞蛾线","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"端详飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=14; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>飞蛾线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>端详飞蛾（克拉克）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    </r>
   </si>
   <si>
     <t>5</t>
@@ -231,7 +297,70 @@
     <t>他的脸和一楼照片上的盖曼.阿门努斯一模一样，但表情完全不同——那照片里的医生目光温和，眉眼间带着学者的谨慎；而此刻坐在电刑椅上的这个男人，嘴角挂着一种近乎享受的微笑，像是刚拆开一件期待已久的礼物。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=16; wherelist={"wheretype":"2","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"飞蛾线","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（克拉克）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=16; wherelist={"wheretype":"2","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>飞蛾线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无视飞蛾（克拉克）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    </r>
   </si>
   <si>
     <t>7</t>
@@ -264,7 +393,70 @@
     <t>这张脸你们见过——在一楼角落的照片墙上、在三楼盖曼的办公室里，在所有飞蛾引导你们前往，而你们也趋之若鹜的火焰之中，在索菲亚内心深处最为恐惧，亦无法轻易割舍的过去之中。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=16; wherelist={"wheretype":"2","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"飞蛾线","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"端详飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=16; wherelist={"wheretype":"2","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>飞蛾线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>端详飞蛾（克拉克）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    </r>
   </si>
   <si>
     <t>10</t>
@@ -461,7 +653,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>sntzm_david4F(3)</t>
+      <t>sntzm_clark4F(3)</t>
     </r>
     <r>
       <rPr>
@@ -704,7 +896,70 @@
     <t>jump(10)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=16; wherelist={"wheretype":"2","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"夜莺线","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"端详飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=10</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=16; wherelist={"wheretype":"2","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>夜莺线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>端详飞蛾（克拉克）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=10</t>
+    </r>
   </si>
   <si>
     <t>60</t>
@@ -713,7 +968,70 @@
     <t>你口中的话刚说出一半，便被他凶险的眼神生生截停在了半空。那不是一张让你熟悉的脸，但其诡谲的笑容里散发出的无形的恶意却让你胃里升起一阵恶寒。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=14; wherelist={"wheretype":"2","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"夜莺线","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=14; wherelist={"wheretype":"2","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>夜莺线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无视飞蛾（克拉克）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    </r>
   </si>
   <si>
     <t>61</t>
@@ -1335,6 +1653,11 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1487,11 +1810,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1800,31 +2118,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1833,124 +2148,130 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2650,15 +2971,15 @@
         <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:12">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2676,7 +2997,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2688,12 +3009,12 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="40.5" spans="1:12">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2711,7 +3032,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -2723,15 +3044,15 @@
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" ht="54" spans="1:12">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2749,7 +3070,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2764,15 +3085,15 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -2787,7 +3108,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -2802,12 +3123,12 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -2825,7 +3146,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -2840,15 +3161,15 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
@@ -2863,7 +3184,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -2878,12 +3199,12 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -2916,12 +3237,12 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" ht="150" spans="1:12">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -2939,7 +3260,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -2954,15 +3275,15 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" ht="28.5" spans="1:12">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
@@ -2977,7 +3298,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -2992,12 +3313,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3030,12 +3351,12 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" ht="150" spans="1:12">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3053,7 +3374,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3065,15 +3386,15 @@
         <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>59</v>
-      </c>
-      <c r="L15" t="s">
         <v>60</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3106,12 +3427,12 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" ht="150" spans="1:12">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3129,7 +3450,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3140,16 +3461,16 @@
       <c r="J17" t="s">
         <v>15</v>
       </c>
-      <c r="L17" t="s">
-        <v>65</v>
+      <c r="L17" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
@@ -3164,7 +3485,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3179,15 +3500,15 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
@@ -3202,7 +3523,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3214,15 +3535,15 @@
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" ht="150" spans="1:12">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3240,7 +3561,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3254,16 +3575,16 @@
       <c r="K20" t="s">
         <v>15</v>
       </c>
-      <c r="L20" t="s">
-        <v>76</v>
+      <c r="L20" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
@@ -3278,7 +3599,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3293,15 +3614,15 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -3316,7 +3637,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3331,12 +3652,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" ht="90" spans="1:12">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3354,7 +3675,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3369,12 +3690,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" ht="54" spans="1:12">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3392,7 +3713,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3404,15 +3725,15 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3445,15 +3766,15 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" ht="90" spans="1:12">
       <c r="A26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
@@ -3468,7 +3789,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3483,12 +3804,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" ht="27" spans="1:12">
       <c r="A27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3506,7 +3827,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3521,21 +3842,21 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3544,7 +3865,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3556,15 +3877,15 @@
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" ht="27" spans="1:12">
       <c r="A29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3573,7 +3894,7 @@
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -3582,7 +3903,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3594,15 +3915,15 @@
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3635,15 +3956,15 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" ht="150" spans="1:12">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
@@ -3658,7 +3979,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3673,12 +3994,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" ht="27" spans="1:12">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3696,7 +4017,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3711,15 +4032,15 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" ht="57" spans="1:12">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
@@ -3734,7 +4055,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3746,15 +4067,15 @@
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3772,7 +4093,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3787,15 +4108,15 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" ht="28.5" spans="1:12">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
@@ -3810,7 +4131,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -3825,15 +4146,15 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -3848,7 +4169,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -3863,12 +4184,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" ht="27" spans="1:12">
       <c r="A37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -3886,7 +4207,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -3901,15 +4222,15 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C38" t="s">
         <v>14</v>
@@ -3924,7 +4245,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -3939,12 +4260,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" ht="55.5" spans="1:12">
       <c r="A39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -3962,7 +4283,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -3973,19 +4294,19 @@
       <c r="J39" t="s">
         <v>15</v>
       </c>
-      <c r="K39" s="2" t="s">
-        <v>137</v>
+      <c r="K39" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="L39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" ht="150" spans="1:12">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C40" t="s">
         <v>14</v>
@@ -4000,7 +4321,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4012,18 +4333,18 @@
         <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" ht="150" spans="1:12">
       <c r="A41" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
@@ -4038,7 +4359,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4050,15 +4371,15 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" ht="70.5" spans="1:12">
       <c r="A42" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4076,7 +4397,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4091,12 +4412,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" ht="28.5" spans="1:12">
       <c r="A43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4114,7 +4435,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4129,15 +4450,15 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B44" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
@@ -4152,7 +4473,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4167,12 +4488,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" ht="40.5" spans="1:12">
       <c r="A45" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4190,7 +4511,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4205,15 +4526,15 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" ht="28.5" spans="1:12">
       <c r="A46" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B46" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -4228,7 +4549,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4243,12 +4564,12 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" ht="27" spans="1:12">
       <c r="A47" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4266,7 +4587,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4281,21 +4602,21 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" ht="42" spans="1:12">
       <c r="A48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4304,7 +4625,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4316,24 +4637,24 @@
         <v>15</v>
       </c>
       <c r="K48" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L48" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" ht="40.5" spans="1:12">
       <c r="A49" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4342,7 +4663,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4354,15 +4675,15 @@
         <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" ht="150" spans="1:12">
       <c r="A50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4380,7 +4701,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4392,15 +4713,15 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L50" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4433,21 +4754,21 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52" ht="90" spans="1:12">
       <c r="A52" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4456,7 +4777,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4468,15 +4789,15 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L52" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53" ht="27" spans="1:12">
       <c r="A53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4485,7 +4806,7 @@
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -4494,7 +4815,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4506,18 +4827,18 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L53" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" ht="42" spans="1:12">
       <c r="A54" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
@@ -4532,7 +4853,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4547,15 +4868,15 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
@@ -4570,7 +4891,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4585,12 +4906,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="56" ht="40.5" spans="1:12">
       <c r="A56" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4608,7 +4929,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4623,15 +4944,15 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" ht="40.5" spans="1:12">
       <c r="A57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B57" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -4646,7 +4967,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4661,15 +4982,15 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" ht="27" spans="1:12">
       <c r="A58" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B58" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
@@ -4684,7 +5005,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4699,12 +5020,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="59" ht="27" spans="1:12">
       <c r="A59" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4722,7 +5043,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4737,12 +5058,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60" ht="54" spans="1:12">
       <c r="A60" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4760,7 +5081,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4772,24 +5093,24 @@
         <v>15</v>
       </c>
       <c r="K60" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L60" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="61" ht="90" spans="1:12">
       <c r="A61" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B61" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -4798,7 +5119,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4810,24 +5131,24 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L61" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="62" ht="28.5" spans="1:12">
       <c r="A62" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -4836,7 +5157,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -4848,15 +5169,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" ht="27" spans="1:12">
       <c r="A63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -4874,7 +5195,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -4889,15 +5210,15 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="64" ht="42" spans="1:12">
       <c r="A64" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -4912,7 +5233,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -4923,16 +5244,16 @@
       <c r="J64" t="s">
         <v>15</v>
       </c>
-      <c r="K64" s="2" t="s">
-        <v>137</v>
+      <c r="K64" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="L64" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="65" ht="150" spans="1:12">
       <c r="A65" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -4950,7 +5271,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -4962,15 +5283,15 @@
         <v>15</v>
       </c>
       <c r="K65" t="s">
-        <v>214</v>
-      </c>
-      <c r="L65" t="s">
         <v>215</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="66" ht="150" spans="1:12">
       <c r="A66" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -4988,7 +5309,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5002,13 +5323,13 @@
       <c r="K66" t="s">
         <v>15</v>
       </c>
-      <c r="L66" t="s">
-        <v>218</v>
+      <c r="L66" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="67" ht="55.5" spans="1:12">
       <c r="A67" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5026,7 +5347,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5041,12 +5362,12 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="68" ht="27" spans="1:12">
       <c r="A68" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5064,7 +5385,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5079,15 +5400,15 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B69" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
@@ -5102,7 +5423,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5117,15 +5438,15 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" ht="28.5" spans="1:12">
       <c r="A70" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -5140,7 +5461,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5152,15 +5473,15 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L70" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" ht="150" spans="1:12">
       <c r="A71" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5168,7 +5489,7 @@
       <c r="C71" t="s">
         <v>14</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E71" t="s">
@@ -5178,7 +5499,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5190,10 +5511,10 @@
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L71" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -5214,122 +5535,122 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -5351,616 +5672,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C13" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C16" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D16" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F16" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B17" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C17" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D17" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F17" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B18" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C18" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D18" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E18" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F18" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B20" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C20" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D20" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E20" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F20" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B21" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C21" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D21" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F21" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B22" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C22" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D22" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E22" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F22" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B23" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C23" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D23" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E23" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F23" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B24" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C24" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D24" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E24" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F24" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B25" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C25" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D25" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E25" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F25" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B26" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C26" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D26" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E26" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F26" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B27" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C27" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D27" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E27" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F27" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B28" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C28" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D28" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E28" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F28" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B29" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C29" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D29" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E29" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F29" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B30" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C30" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D30" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E30" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F30" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B31" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C31" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D31" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
